--- a/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>In a patient with paroxysmal atrial fibrillation and a CHA2DS2-VASc score &gt;3, anticoagulant therapy is indicated and may be carried out with DOACs:</t>
+          <t>In a patient with paroxysmal atrial fibrillation and a CHA2DS2-VASc score &gt;3, anticoagulant therapy is indicated and may be administered with DOACs.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Airways, Breathing, Circulation: perform an assessment of vital functions when a patient is unconscious. Certainly, performing an ECG is not a priority action to ensure proper oxygenation of the patient, much less cardioversion (a valid option if an analysis of the cardiac rhythm reveals a supraventricular arrhythmia such as atrial fibrillation) or an echocardiogram, a second-line examination in the cardiological risk stratification of a patient. Volume replacement should be considered when cardiac pump function is ensured, but in this patient the priority is to support tissue oxygenation, which has been lost due to respiratory arrest. Correct answer A. Difficulty: Low</t>
+          <t>Initiate volume replacement</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>All of the following drug classes are associated with an increased risk of falls, EXCEPT:</t>
+          <t>All of the following drug classes are associated with an increased risk of falls, EXCEPT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Which of the following investigations is NOT recommended in the first-level evaluation of a patient with recurrent falls:</t>
+          <t>Which of the following investigations is NOT recommended in the first-level evaluation of a patient with recurrent falls</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The elderly patient presenting with a condition of sarcopenia:</t>
+          <t>The elderly patient presenting with a condition of sarcopenia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>In a 60-year-old patient with HER-2-positive gastric carcinoma with liver metastases (stage IV), which of the following treatments is most indicated:</t>
+          <t>In a 60-year-old patient with HER-2-positive metastatic gastric carcinoma with hepatic metastases (stage IV), which of the following treatments is most indicated:</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A 32-year-old young woman, who experienced a spontaneous abortion in the preceding weeks, presents with a non-scarring hairless patch in the right parietal region. The suspected diagnosis is:</t>
+          <t>A 32-year-old young woman, who experienced a spontaneous abortion in the preceding weeks, presents with a non-scarring hairless patch in the right parietal region. The suspected diagnosis is</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>According to the Ann Arbor staging system, bone marrow involvement in a patient with Hodgkin lymphoma defines clinical stage:</t>
+          <t>According to the Ann Arbor staging system, bone marrow involvement in a patient with Hodgkin lymphoma defines clinical stage</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A 78-year-old woman presents to the hematology outpatient clinic, referred by her primary care physician for a complete blood count finding of Hb 7.8 g/dL, leukocytes 3,200/mm3 with neutrophils 1,000/mm3, platelets 89,000/mm3. MCV 112 fL, vitamin B12 and folate within the normal range. With a suspicion of myelodysplastic syndrome, which of the following tests is NOT indicated in the diagnostic workup?</t>
+          <t>A 78-year-old woman presents to the hematology outpatient clinic, referred by her primary care physician for a complete blood count finding of Hb 7.8 g/dL, leukocytes 3,200/mm3 with neutrophils 1,000/mm3, platelets 89,000/mm3. MCV 112 fL, with vitamin B12 and folate within the normal range. Given the suspicion of myelodysplastic syndrome, which of the following tests is NOT indicated in the diagnostic workup?</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A 49-year-old woman presents to her primary care physician with a fasting blood glucose value of 146 mg/dl and a glycated hemoglobin of 54 mmol/mol. She has a positive family history of diabetes and hypertension and is herself hypertensive, being treated with an ACE inhibitor. She has a body mass index of 28 kg/m2 and also presents with hypertriglyceridemia. An abdominal ultrasound shows hepatic steatosis, with normal pancreas and adrenal glands. What is the most likely diagnosis?</t>
+          <t>A 49-year-old woman presents to her primary care physician with a fasting blood glucose of 146 mg/dL and a glycated hemoglobin of 54 mmol/mol. She has a positive family history of diabetes and hypertension and is herself hypertensive, treated with an ACE inhibitor. She has a body mass index of 28 kg/m², and also presents with hypertriglyceridemia. An abdominal ultrasound shows hepatic steatosis, with normal pancreas and adrenal glands. What is the most likely diagnosis?</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A 24-year-old woman with galactorrhea presents to the endocrinology clinic. The investigations performed show the presence of a prolactin-secreting pituitary microadenoma. There are no visual disturbances, but menstrual cycle alterations and breast tenderness coexist. Which of the following is the indicated treatment?</t>
+          <t>A 24-year-old woman with galactorrhea presents to the endocrinology clinic. The workup reveals a prolactin-secreting pituitary microadenoma. There are no visual disturbances, but menstrual cycle irregularities and breast tenderness are also present. Which of the following is the indicated treatment?</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>In COVID-19 pneumonia, the radiological picture does not always show consolidations, and not effusions; in amiodarone-induced lung injury, a fibrotic pattern develops. The option regarding COPD may indeed be characterized by pleural effusion, but associated with emphysematous bullae, which are not mentioned in the question. The picture therefore more likely concerns heart failure. Difficulty</t>
+          <t>Acute exacerbation of COPD</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>What is meant by erythema toxicum neonatorum:</t>
+          <t>What is meant by erythema toxicum neonatorum</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>In jaundice, the suspicion that it may be obstructive arises when:</t>
+          <t>In jaundice, the suspicion that it may be obstructive arises when</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Whipple's triad, a set of three elements suggestive of the presence of an insulinoma, typically manifests:</t>
+          <t>Whipple's triad, a set of three elements suggestive of the presence of an insulinoma, typically manifests</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Gallstone ileus is a form of:</t>
+          <t>Gallstone ileus is a form of</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>after a prolonged labor it is more difficult for the uterus to contract in response to the administration of uterotonics). Maternal hypothyroidism, on the other hand, does not increase the risk of postpartum hemorrhage. (Answer A correct) Difficulty: Medium</t>
+          <t>Prolonged labor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A 32-year-old woman in the postpartum period presents with persistent lochia three months after delivery, which progressively becomes more abundant, malodorous, and associated with evening fever. She undergoes a pelvic ultrasound that demonstrates a focal endometrial thickening of 25 mm. The most likely diagnosis is:</t>
+          <t>A 32-year-old woman in the puerperium presents with persistent lochia three months after delivery, which progressively becomes more abundant, malodorous, and associated with evening fever. She undergoes a pelvic ultrasound that demonstrates a focal endometrial thickening of 25 mm. The most likely diagnosis is:</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>The lamina papyracea is a thin bony plate that forms:</t>
+          <t>The lamina papyracea is a thin bony plate that forms</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Benign paroxysmal positional vertigo is characterized by:</t>
+          <t>Benign paroxysmal positional vertigo is characterized by</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>The Wright test is a specific test for diagnosing thoracic outlet syndrome, and a supernumerary cervical rib is a pathognomonic risk factor for this syndrome. Difficulty: Easy</t>
+          <t>Thoracic outlet syndrome</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>A young man presents with multiple hamartomatous polyps of the intestine, mucocutaneous hyperpigmentation, especially of the oral mucosa. The most likely diagnosis is:</t>
+          <t>A young man presents with multiple hamartomatous polyps of the intestine, mucocutaneous hyperpigmentation, especially of the oral mucosa. The most likely diagnosis is</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>A 74-year-old patient, bedridden after surgery for a femoral fracture, presents to the Emergency Department for syncope, chest pain, and sudden-onset dyspnea. The patient also presents with fever and a hacking cough. With a suspicion of a bronchopneumonic process associated with pulmonary embolism, which of the following statements is correct?</t>
+          <t>A 74-year-old patient, bedridden after surgery for a femoral fracture, presents to the Emergency Department with syncope, chest pain, and sudden-onset dyspnea. The patient also presents with fever and a hacking cough. Given the suspicion of a bronchopneumonic process associated with pulmonary embolism, which of the following statements is correct?</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Bronchial provocation test, for measuring nitric oxide present in exhaled air. One must always consider the cost-benefit ratio and the actual usefulness of performing a diagnostic test, useful for the risk stratification of a patient</t>
+          <t>Bronchial provocation test, for the measurement of nitric oxide present in exhaled air. One must always consider the cost-benefit ratio and the actual usefulness of performing a diagnostic test, useful for the risk stratification of a patient</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>A 70-year-old patient undergoing general anesthesia with orotracheal intubation develops severe desaturation with pinkish fluid coming out of the endotracheal tube and, on auscultation, diffuse crackles over both hemithoraces, leading to suspicion of pulmonary edema. Among other measures regarding the ventilator settings, it is appropriate to:</t>
+          <t>A 70-year-old patient undergoing general anesthesia with orotracheal intubation develops severe desaturation with pinkish fluid emerging from the endotracheal tube and, on auscultation, diffuse crackles over both hemithoraces, raising suspicion of pulmonary edema. Among other measures regarding the established ventilator settings, it is appropriate to:</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>In a polytrauma patient diagnosed with intracerebral hematoma, pneumothorax, and splenic rupture, the sequence of interventions is:</t>
+          <t>In a polytrauma patient diagnosed with intracerebral hematoma, pneumothorax, and splenic rupture, the sequence of interventions is</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Indicate the correct statement regarding the tracheostomy procedure:</t>
+          <t>Indicate the correct statement regarding the tracheostomy procedure.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Phase II clinical trials:</t>
+          <t>Phase II clinical trials</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Regarding the indicators currently used internationally to measure the burden of disease, indicate which of the following statements is FALSE:</t>
+          <t>Regarding indicators currently used internationally to measure the burden of disease, indicate which of the following statements is FALSE:</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>In the case of vaccine-preventable diseases, the goal of eradication is achieved when:</t>
+          <t>In the case of vaccine-preventable diseases, the goal of eradication is achieved when</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>The anti-SARS-CoV-2 vaccines, both mRNA and viral vector, used for the vaccination campaign in Italy:</t>
+          <t>The anti-SARS-CoV-2 vaccines, both mRNA and viral vector, used for the vaccination campaign in Italy</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Byssinosis is:</t>
+          <t>Byssinosis is</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>According to the IARC, formaldehyde:</t>
+          <t>According to the IARC, formaldehyde</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Following a fall from scaffolding at the construction site where he was working, a 40-year-old man presents to the Emergency Department with multiple injuries (polytrauma) and a prognosis exceeding 40 days. Since the injuries are likely the result of negligence, the physician must:</t>
+          <t>Following a fall from scaffolding at the construction site where he was working, a 40-year-old man presents to the Emergency Department with multiple injuries (polytrauma) and a prognosis exceeding 40 days. Since the injuries are likely the result of negligence, the physician must</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>An 80-year-old man, suffering from metastatic cancer for several years, dies at his home. The family members contact the treating physician requesting, if possible, to schedule the funeral for that same afternoon. The treating physician:</t>
+          <t>An 80-year-old man, who had suffered from metastatic malignancy for several years, dies at his home. The family members contact the treating physician, requesting that, if possible, the funeral be scheduled for that same afternoon. The treating physician:</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>The standard deviation is obtained as:</t>
+          <t>The standard deviation is obtained as</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Oncology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Oncology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Oncology</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Nephrology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Nephrology</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Nephrology</t>
+          <t>Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Endocrinology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Endocrinology</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Medical Genetics</t>
+          <t>Neurology and Neurosurgery; Pediatrics</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Pediatrics; General Surgery</t>
+          <t>General Surgery; Pediatrics</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Nephrology; Medical Genetics</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>General Surgery; Oncology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Neurology and Neurosurgery</t>
+          <t>Orthopedics and Traumatology; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Hematology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Immunology and Rheumatology</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Clinical Nutrition</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; General Surgery</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Forensic Medicine</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Oncology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Oncology</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Immunology and Rheumatology</t>
+          <t>Anesthesia and Intensive Care; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Oncology; Medical Genetics</t>
+          <t>Medical Genetics; Oncology</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Infectious Diseases</t>
+          <t>Infectious Diseases; Hygiene, Epidemiology and Statistics</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Infectious Diseases</t>
+          <t>Infectious Diseases; Hygiene, Epidemiology and Statistics</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Occupational Medicine; Pulmonology and Thoracic Surgery</t>
+          <t>Occupational Medicine</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2022_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -544,6 +549,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -602,6 +612,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -660,6 +675,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -718,6 +738,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +801,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -834,6 +864,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +927,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -950,6 +990,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1008,6 +1053,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1066,6 +1116,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1124,6 +1179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1182,6 +1242,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1242,10 +1307,15 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>images/2022/ssm2022153.png</t>
         </is>
@@ -1308,6 +1378,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1366,6 +1441,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1424,6 +1504,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1482,6 +1567,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1540,6 +1630,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1598,6 +1693,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1656,6 +1756,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1714,6 +1819,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1772,6 +1882,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1830,6 +1945,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1888,6 +2008,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1946,6 +2071,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2004,6 +2134,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2062,6 +2197,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2120,6 +2260,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2178,6 +2323,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2236,6 +2386,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2294,6 +2449,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2352,6 +2512,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2410,6 +2575,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2468,6 +2638,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2526,6 +2701,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2584,6 +2764,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2642,6 +2827,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2700,6 +2890,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2758,6 +2953,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2816,6 +3016,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2874,6 +3079,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2932,6 +3142,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2990,6 +3205,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3048,6 +3268,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3106,6 +3331,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3164,6 +3394,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3222,6 +3457,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3280,6 +3520,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3338,6 +3583,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3396,6 +3646,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3454,6 +3709,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3512,6 +3772,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3570,6 +3835,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3628,6 +3898,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3686,6 +3961,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3744,6 +4024,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3802,6 +4087,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3860,6 +4150,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3918,6 +4213,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3976,6 +4276,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4034,6 +4339,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4092,6 +4402,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4150,6 +4465,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4208,6 +4528,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4266,6 +4591,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4324,6 +4654,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4382,6 +4717,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4440,6 +4780,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4498,6 +4843,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4556,6 +4906,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4614,6 +4969,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4672,6 +5032,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4730,6 +5095,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4788,6 +5158,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4846,6 +5221,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4904,6 +5284,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4962,6 +5347,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5020,6 +5410,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5078,6 +5473,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5136,6 +5536,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5194,6 +5599,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5252,6 +5662,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5312,10 +5727,15 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>images/2022/ssm2022223.png</t>
         </is>
@@ -5380,10 +5800,15 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>images/2022/ssm2022224.png</t>
         </is>
@@ -5448,10 +5873,15 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>Knee arthroscopy image and knee MRI</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>images/2022/ssm2022225.png</t>
         </is>
@@ -5514,6 +5944,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5572,6 +6007,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5630,6 +6070,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5688,6 +6133,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5746,6 +6196,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5804,6 +6259,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5862,6 +6322,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5920,6 +6385,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5978,6 +6448,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6036,6 +6511,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6094,6 +6574,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6152,6 +6637,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6210,6 +6700,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6268,6 +6763,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6326,6 +6826,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6384,6 +6889,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6442,6 +6952,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6500,6 +7015,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6558,6 +7078,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6616,6 +7141,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6674,6 +7204,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6732,6 +7267,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6790,6 +7330,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6848,6 +7393,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6906,6 +7456,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6964,6 +7519,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7022,6 +7582,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7080,6 +7645,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7138,6 +7708,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7196,6 +7771,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7254,6 +7834,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7312,6 +7897,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7370,6 +7960,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7428,6 +8023,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7486,6 +8086,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7544,6 +8149,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7602,6 +8212,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7660,6 +8275,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7718,6 +8338,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7776,6 +8401,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7834,6 +8464,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7892,6 +8527,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7950,6 +8590,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8008,6 +8653,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8066,6 +8716,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8124,6 +8779,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8182,6 +8842,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8240,6 +8905,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8298,6 +8968,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8356,6 +9031,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8414,6 +9094,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8472,6 +9157,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8530,6 +9220,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8588,6 +9283,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8644,6 +9344,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
